--- a/PTBR/Lang/PTBR/Game/Research.xlsx
+++ b/PTBR/Lang/PTBR/Game/Research.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pedra da Cidade</t>
+          <t>Pedra do Lar</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Desenvolvimento Residencial</t>
+          <t>Desenvolvimento do Lar</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Departamento de Justiça</t>
+          <t>Departamento de Leis</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Departamento da Economia</t>
+          <t>Departamento de Economia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano de Testes A</t>
+          <t>Plano de Teste A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano de Testes B</t>
+          <t>Plano de Teste B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
